--- a/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,74</t>
+          <t>0,45; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,88</t>
+          <t>0,98; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,99</t>
+          <t>0,96; 4,8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,95</t>
+          <t>0,62; 5,83</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,52</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 6,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,99</t>
+          <t>0,64; 6,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,99</t>
+          <t>0,28; 2,94</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,43</t>
+          <t>1,4; 7,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,8</t>
+          <t>1,03; 3,98</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,85</t>
+          <t>1,09; 2,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,05</t>
+          <t>0,59; 2,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,19</t>
+          <t>0,94; 2,16</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2456</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>573; 7243</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1240; 8628</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2421; 12134</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3047</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5402</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4947</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>757; 7092</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1564</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 856</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8290</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8184</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2840</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2812</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3660</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>771; 7731</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>762; 7982</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1836; 9290</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4960</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2905; 11263</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20477</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>7131; 19227</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4420; 15600</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13156; 30099</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,75</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,82</t>
+          <t>1,12; 7,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,8</t>
+          <t>1,1; 4,75</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,83</t>
+          <t>0,62; 5,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,46</t>
+          <t>0,66; 6,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,94</t>
+          <t>0,29; 2,97</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,1</t>
+          <t>1,43; 7,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,98</t>
+          <t>0,95; 3,84</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,95</t>
+          <t>1,05; 2,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,1</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,16</t>
+          <t>0,98; 2,21</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>573; 7243</t>
+          <t>0; 7274</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1240; 8628</t>
+          <t>1421; 9803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2421; 12134</t>
+          <t>2769; 12000</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5402</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4947</t>
+          <t>0; 5882</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>757; 7092</t>
+          <t>758; 6989</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 856</t>
+          <t>0; 918</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8290</t>
+          <t>0; 7623</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8184</t>
+          <t>0; 7317</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2840</t>
+          <t>0; 2966</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2812</t>
+          <t>0; 2319</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3660</t>
+          <t>0; 3354</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>771; 7731</t>
+          <t>787; 7739</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>762; 7982</t>
+          <t>798; 8051</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1836; 9290</t>
+          <t>1872; 9733</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>0; 4961</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2905; 11263</t>
+          <t>2690; 10868</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7131; 19227</t>
+          <t>6830; 19183</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4420; 15600</t>
+          <t>4295; 14694</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13156; 30099</t>
+          <t>13705; 30855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,97; 6,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,75</t>
+          <t>0,68; 6,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,75</t>
+          <t>1,19; 5,22</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,92</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 9,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,75</t>
+          <t>0,62; 6,04</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,69; 7,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,97</t>
+          <t>0,31; 3,33</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,44</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>1,44; 7,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,84</t>
+          <t>0,93; 3,76</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,94</t>
+          <t>0,54; 2,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>1,2; 3,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,21</t>
+          <t>1,04; 2,27</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>5428</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7274</t>
+          <t>1114; 7696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1421; 9803</t>
+          <t>682; 6241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2769; 12000</t>
+          <t>2565; 11203</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2850</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 5066</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5882</t>
+          <t>0; 5281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>758; 6989</t>
+          <t>698; 6790</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1848</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 918</t>
+          <t>0; 7839</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7623</t>
+          <t>0; 2196</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7317</t>
+          <t>0; 7485</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>596</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1123</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2966</t>
+          <t>0; 3272</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2319</t>
+          <t>0; 2995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 4003</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3174</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>787; 7739</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>819; 8821</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>798; 8051</t>
+          <t>798; 8506</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5646</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1872; 9733</t>
+          <t>0; 5460</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4961</t>
+          <t>2003; 10314</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2690; 10868</t>
+          <t>2729; 11099</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20068</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6830; 19183</t>
+          <t>3669; 14550</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4295; 14694</t>
+          <t>7390; 18687</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13705; 30855</t>
+          <t>13498; 29527</t>
         </is>
       </c>
     </row>
